--- a/data/gravel/Trek Checkpoint ALR (gen 3) 2025.xlsx
+++ b/data/gravel/Trek Checkpoint ALR (gen 3) 2025.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel copy/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB994637-FE62-DD4C-B32B-682F904D19C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{416289C3-A85D-464B-A55A-240D2CE177B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2200" yWindow="3060" windowWidth="26600" windowHeight="13160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="115">
   <si>
     <t>brand</t>
   </si>
@@ -360,6 +360,24 @@
   </si>
   <si>
     <t>Checkpoint ALR (gen 3)</t>
+  </si>
+  <si>
+    <t>class</t>
+  </si>
+  <si>
+    <t>gravel</t>
+  </si>
+  <si>
+    <t>handlebar</t>
+  </si>
+  <si>
+    <t>drop bar</t>
+  </si>
+  <si>
+    <t>fork</t>
+  </si>
+  <si>
+    <t>rigid</t>
   </si>
 </sst>
 </file>
@@ -712,7 +730,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:X67"/>
+  <dimension ref="A1:X70"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1815,176 +1833,179 @@
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>58</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>106</v>
+        <v>109</v>
+      </c>
+      <c r="B33" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>59</v>
+        <v>111</v>
       </c>
       <c r="B34" t="s">
-        <v>60</v>
+        <v>112</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>61</v>
+        <v>113</v>
+      </c>
+      <c r="B35" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>62</v>
-      </c>
-      <c r="B36" t="s">
-        <v>53</v>
+        <v>58</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>63</v>
+        <v>59</v>
+      </c>
+      <c r="B37" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>64</v>
-      </c>
-      <c r="B38" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B39" t="s">
-        <v>67</v>
+        <v>53</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>68</v>
-      </c>
-      <c r="B40" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="B41" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="B42" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="B43" t="s">
-        <v>49</v>
+        <v>67</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B44" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>75</v>
+        <v>70</v>
+      </c>
+      <c r="B45" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B46" t="s">
-        <v>77</v>
+        <v>49</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B47" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>80</v>
-      </c>
-      <c r="B48" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="B49" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="B50" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>85</v>
+        <v>80</v>
+      </c>
+      <c r="B51" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="B52" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B53" t="s">
-        <v>60</v>
+        <v>83</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="B55" t="s">
-        <v>60</v>
+        <v>87</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B56" t="s">
         <v>60</v>
@@ -1992,86 +2013,107 @@
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>92</v>
-      </c>
-      <c r="B57" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="B58" t="s">
-        <v>95</v>
+        <v>60</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="B59" t="s">
-        <v>95</v>
+        <v>60</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="B60" t="s">
-        <v>60</v>
+        <v>93</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B61" t="s">
-        <v>60</v>
+        <v>95</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>99</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>60</v>
+        <v>96</v>
+      </c>
+      <c r="B62" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>100</v>
-      </c>
-      <c r="B63" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B63" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>101</v>
-      </c>
-      <c r="B64">
-        <v>1049.99</v>
+        <v>98</v>
+      </c>
+      <c r="B64" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>102</v>
-      </c>
-      <c r="B65">
-        <v>1499.99</v>
+        <v>99</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>103</v>
+        <v>100</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
+        <v>101</v>
+      </c>
+      <c r="B67">
+        <v>1049.99</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>102</v>
+      </c>
+      <c r="B68">
+        <v>1499.99</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
         <v>104</v>
       </c>
-      <c r="B67" t="s">
+      <c r="B70" t="s">
         <v>105</v>
       </c>
     </row>

--- a/data/gravel/Trek Checkpoint ALR (gen 3) 2025.xlsx
+++ b/data/gravel/Trek Checkpoint ALR (gen 3) 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel copy/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{416289C3-A85D-464B-A55A-240D2CE177B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A53933A-77B4-B642-818A-9F53DCBEABE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2200" yWindow="3060" windowWidth="26600" windowHeight="13160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/data/gravel/Trek Checkpoint ALR (gen 3) 2025.xlsx
+++ b/data/gravel/Trek Checkpoint ALR (gen 3) 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10905"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A53933A-77B4-B642-818A-9F53DCBEABE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE165246-B37A-D544-A3C9-D24B695257BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2200" yWindow="3060" windowWidth="26600" windowHeight="13160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="115">
   <si>
     <t>brand</t>
   </si>
@@ -2028,9 +2028,6 @@
       <c r="A59" t="s">
         <v>91</v>
       </c>
-      <c r="B59" t="s">
-        <v>60</v>
-      </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">

--- a/data/gravel/Trek Checkpoint ALR (gen 3) 2025.xlsx
+++ b/data/gravel/Trek Checkpoint ALR (gen 3) 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10905"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10921"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE165246-B37A-D544-A3C9-D24B695257BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DC8B67A-264B-F045-A7ED-491C407BB7D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2200" yWindow="3060" windowWidth="26600" windowHeight="13160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="116">
   <si>
     <t>brand</t>
   </si>
@@ -356,9 +356,6 @@
     <t>aluminum</t>
   </si>
   <si>
-    <t>a8:h30</t>
-  </si>
-  <si>
     <t>Checkpoint ALR (gen 3)</t>
   </si>
   <si>
@@ -378,6 +375,12 @@
   </si>
   <si>
     <t>rigid</t>
+  </si>
+  <si>
+    <t>frame_weight</t>
+  </si>
+  <si>
+    <t>a8:h31</t>
   </si>
 </sst>
 </file>
@@ -730,7 +733,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:X70"/>
+  <dimension ref="A1:X71"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -749,7 +752,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.3">
@@ -781,7 +784,7 @@
         <v>9</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.3">
@@ -1603,30 +1606,10 @@
       </c>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>46</v>
-      </c>
-      <c r="B23" t="s">
-        <v>46</v>
-      </c>
-      <c r="C23">
-        <v>415</v>
-      </c>
-      <c r="D23">
-        <v>415</v>
-      </c>
-      <c r="E23">
-        <v>415</v>
-      </c>
-      <c r="F23">
-        <v>415</v>
-      </c>
-      <c r="G23">
-        <v>415</v>
-      </c>
-      <c r="H23">
-        <v>415</v>
-      </c>
+      <c r="A23" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B23" s="2"/>
       <c r="J23" s="2"/>
       <c r="K23" s="3"/>
       <c r="L23" s="3"/>
@@ -1637,10 +1620,28 @@
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B24" t="s">
-        <v>47</v>
+        <v>46</v>
+      </c>
+      <c r="C24">
+        <v>415</v>
+      </c>
+      <c r="D24">
+        <v>415</v>
+      </c>
+      <c r="E24">
+        <v>415</v>
+      </c>
+      <c r="F24">
+        <v>415</v>
+      </c>
+      <c r="G24">
+        <v>415</v>
+      </c>
+      <c r="H24">
+        <v>415</v>
       </c>
       <c r="J24" s="2"/>
       <c r="K24" s="3"/>
@@ -1652,28 +1653,10 @@
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B25" t="s">
-        <v>48</v>
-      </c>
-      <c r="C25">
-        <v>70</v>
-      </c>
-      <c r="D25">
-        <v>80</v>
-      </c>
-      <c r="E25">
-        <v>80</v>
-      </c>
-      <c r="F25">
-        <v>90</v>
-      </c>
-      <c r="G25">
-        <v>90</v>
-      </c>
-      <c r="H25">
-        <v>100</v>
+        <v>47</v>
       </c>
       <c r="J25" s="2"/>
       <c r="K25" s="3"/>
@@ -1685,10 +1668,28 @@
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B26" t="s">
-        <v>50</v>
+        <v>48</v>
+      </c>
+      <c r="C26">
+        <v>70</v>
+      </c>
+      <c r="D26">
+        <v>80</v>
+      </c>
+      <c r="E26">
+        <v>80</v>
+      </c>
+      <c r="F26">
+        <v>90</v>
+      </c>
+      <c r="G26">
+        <v>90</v>
+      </c>
+      <c r="H26">
+        <v>100</v>
       </c>
       <c r="J26" s="2"/>
       <c r="K26" s="3"/>
@@ -1700,28 +1701,10 @@
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B27" t="s">
-        <v>51</v>
-      </c>
-      <c r="C27">
-        <v>42</v>
-      </c>
-      <c r="D27">
-        <v>42</v>
-      </c>
-      <c r="E27">
-        <v>42</v>
-      </c>
-      <c r="F27">
-        <v>42</v>
-      </c>
-      <c r="G27">
-        <v>42</v>
-      </c>
-      <c r="H27">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="J27" s="2"/>
       <c r="K27" s="3"/>
@@ -1733,28 +1716,28 @@
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B28" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C28">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="D28">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="E28">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="F28">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="G28">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="H28">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="J28" s="2"/>
       <c r="K28" s="3"/>
@@ -1766,28 +1749,28 @@
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B29" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C29">
-        <v>143</v>
+        <v>50</v>
       </c>
       <c r="D29">
-        <v>158</v>
+        <v>50</v>
       </c>
       <c r="E29">
-        <v>164</v>
+        <v>50</v>
       </c>
       <c r="F29">
-        <v>177</v>
+        <v>50</v>
       </c>
       <c r="G29">
-        <v>188</v>
+        <v>50</v>
       </c>
       <c r="H29">
-        <v>194</v>
+        <v>50</v>
       </c>
       <c r="J29" s="2"/>
       <c r="K29" s="3"/>
@@ -1799,115 +1782,140 @@
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
+        <v>54</v>
+      </c>
+      <c r="B30" t="s">
+        <v>54</v>
+      </c>
+      <c r="C30">
+        <v>143</v>
+      </c>
+      <c r="D30">
+        <v>158</v>
+      </c>
+      <c r="E30">
+        <v>164</v>
+      </c>
+      <c r="F30">
+        <v>177</v>
+      </c>
+      <c r="G30">
+        <v>188</v>
+      </c>
+      <c r="H30">
+        <v>194</v>
+      </c>
+      <c r="J30" s="2"/>
+      <c r="K30" s="3"/>
+      <c r="L30" s="3"/>
+      <c r="M30" s="3"/>
+      <c r="N30" s="3"/>
+      <c r="O30" s="3"/>
+      <c r="P30" s="3"/>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
         <v>55</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B31" t="s">
         <v>55</v>
       </c>
-      <c r="C30">
+      <c r="C31">
         <v>158</v>
       </c>
-      <c r="D30">
+      <c r="D31">
         <v>164</v>
       </c>
-      <c r="E30">
+      <c r="E31">
         <v>177</v>
       </c>
-      <c r="F30">
+      <c r="F31">
         <v>188</v>
       </c>
-      <c r="G30">
+      <c r="G31">
         <v>194</v>
       </c>
-      <c r="H30">
+      <c r="H31">
         <v>203</v>
-      </c>
-    </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
-        <v>56</v>
-      </c>
-      <c r="B32" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>109</v>
+        <v>56</v>
       </c>
       <c r="B33" t="s">
-        <v>110</v>
+        <v>57</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B34" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="B35" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>58</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>106</v>
+        <v>112</v>
+      </c>
+      <c r="B36" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>59</v>
-      </c>
-      <c r="B37" t="s">
-        <v>60</v>
+        <v>58</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>61</v>
+        <v>59</v>
+      </c>
+      <c r="B38" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>62</v>
-      </c>
-      <c r="B39" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>63</v>
+        <v>62</v>
+      </c>
+      <c r="B40" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>64</v>
-      </c>
-      <c r="B41" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B42" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B43" t="s">
         <v>67</v>
@@ -1915,76 +1923,76 @@
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B44" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B45" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B46" t="s">
-        <v>49</v>
+        <v>71</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B47" t="s">
-        <v>74</v>
+        <v>49</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>75</v>
+        <v>73</v>
+      </c>
+      <c r="B48" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>76</v>
-      </c>
-      <c r="B49" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B50" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B51" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B52" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B53" t="s">
         <v>83</v>
@@ -1992,62 +2000,62 @@
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>85</v>
+        <v>84</v>
+      </c>
+      <c r="B54" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>86</v>
-      </c>
-      <c r="B55" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B56" t="s">
-        <v>60</v>
+        <v>87</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>89</v>
+        <v>88</v>
+      </c>
+      <c r="B57" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>90</v>
-      </c>
-      <c r="B58" t="s">
-        <v>60</v>
+        <v>89</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>91</v>
+        <v>90</v>
+      </c>
+      <c r="B59" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>92</v>
-      </c>
-      <c r="B60" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B61" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B62" t="s">
         <v>95</v>
@@ -2055,15 +2063,15 @@
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B63" t="s">
-        <v>60</v>
+        <v>95</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B64" t="s">
         <v>60</v>
@@ -2071,15 +2079,15 @@
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>99</v>
-      </c>
-      <c r="B65" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B65" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>60</v>
@@ -2087,30 +2095,38 @@
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>101</v>
-      </c>
-      <c r="B67">
-        <v>1049.99</v>
+        <v>100</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B68">
-        <v>1499.99</v>
+        <v>1049.99</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>103</v>
+        <v>102</v>
+      </c>
+      <c r="B69">
+        <v>1499.99</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
         <v>104</v>
       </c>
-      <c r="B70" t="s">
+      <c r="B71" t="s">
         <v>105</v>
       </c>
     </row>

--- a/data/gravel/Trek Checkpoint ALR (gen 3) 2025.xlsx
+++ b/data/gravel/Trek Checkpoint ALR (gen 3) 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10921"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10928"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DC8B67A-264B-F045-A7ED-491C407BB7D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BCB85D0-1587-0E48-A8CF-234A6778EFB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2200" yWindow="3060" windowWidth="26600" windowHeight="13160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="115">
   <si>
     <t>brand</t>
   </si>
@@ -234,9 +234,6 @@
   </si>
   <si>
     <t>fork_suspension</t>
-  </si>
-  <si>
-    <t>no</t>
   </si>
   <si>
     <t>stem_suspension</t>
@@ -752,7 +749,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.3">
@@ -784,7 +781,7 @@
         <v>9</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.3">
@@ -1607,7 +1604,7 @@
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B23" s="2"/>
       <c r="J23" s="2"/>
@@ -1849,26 +1846,26 @@
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
+        <v>107</v>
+      </c>
+      <c r="B34" t="s">
         <v>108</v>
-      </c>
-      <c r="B34" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
+        <v>109</v>
+      </c>
+      <c r="B35" t="s">
         <v>110</v>
-      </c>
-      <c r="B35" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
+        <v>111</v>
+      </c>
+      <c r="B36" t="s">
         <v>112</v>
-      </c>
-      <c r="B36" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
@@ -1876,7 +1873,7 @@
         <v>58</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
@@ -1917,37 +1914,28 @@
       <c r="A43" t="s">
         <v>66</v>
       </c>
-      <c r="B43" t="s">
-        <v>67</v>
-      </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>68</v>
-      </c>
-      <c r="B44" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>69</v>
-      </c>
-      <c r="B45" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
+        <v>69</v>
+      </c>
+      <c r="B46" t="s">
         <v>70</v>
-      </c>
-      <c r="B46" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B47" t="s">
         <v>49</v>
@@ -1955,73 +1943,73 @@
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
+        <v>72</v>
+      </c>
+      <c r="B48" t="s">
         <v>73</v>
-      </c>
-      <c r="B48" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
+        <v>75</v>
+      </c>
+      <c r="B50" t="s">
         <v>76</v>
-      </c>
-      <c r="B50" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
+        <v>77</v>
+      </c>
+      <c r="B51" t="s">
         <v>78</v>
-      </c>
-      <c r="B51" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
+        <v>79</v>
+      </c>
+      <c r="B52" t="s">
         <v>80</v>
-      </c>
-      <c r="B52" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
+        <v>81</v>
+      </c>
+      <c r="B53" t="s">
         <v>82</v>
-      </c>
-      <c r="B53" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B54" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
+        <v>85</v>
+      </c>
+      <c r="B56" t="s">
         <v>86</v>
-      </c>
-      <c r="B56" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B57" t="s">
         <v>60</v>
@@ -2029,12 +2017,12 @@
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B59" t="s">
         <v>60</v>
@@ -2042,36 +2030,36 @@
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
+        <v>91</v>
+      </c>
+      <c r="B61" t="s">
         <v>92</v>
-      </c>
-      <c r="B61" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
+        <v>93</v>
+      </c>
+      <c r="B62" t="s">
         <v>94</v>
-      </c>
-      <c r="B62" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B63" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B64" t="s">
         <v>60</v>
@@ -2079,7 +2067,7 @@
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B65" t="s">
         <v>60</v>
@@ -2087,7 +2075,7 @@
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>60</v>
@@ -2095,7 +2083,7 @@
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>60</v>
@@ -2103,7 +2091,7 @@
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B68">
         <v>1049.99</v>
@@ -2111,7 +2099,7 @@
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B69">
         <v>1499.99</v>
@@ -2119,15 +2107,15 @@
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
+        <v>103</v>
+      </c>
+      <c r="B71" t="s">
         <v>104</v>
-      </c>
-      <c r="B71" t="s">
-        <v>105</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Trek Checkpoint ALR (gen 3) 2025.xlsx
+++ b/data/gravel/Trek Checkpoint ALR (gen 3) 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BCB85D0-1587-0E48-A8CF-234A6778EFB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49FBB5B8-0654-6F42-9B4D-6FE0C1A9B6F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2200" yWindow="3060" windowWidth="26600" windowHeight="13160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="34780" yWindow="-21340" windowWidth="26600" windowHeight="13160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="116">
   <si>
     <t>brand</t>
   </si>
@@ -56,9 +56,6 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://www.trekbikes.com/us/en_US/bikes/bikepacking-touring-bikes/checkpoint/checkpoint-sl/checkpoint-sl-7-axs-gen-3/p/55097/?colorCode=reddark</t>
-  </si>
-  <si>
     <t>13-Jul-2025</t>
   </si>
   <si>
@@ -378,6 +375,12 @@
   </si>
   <si>
     <t>a8:h31</t>
+  </si>
+  <si>
+    <t>https://www.trekbikes.com/us/en_US/bikes/bikepacking-touring-bikes/checkpoint/checkpoint-alr/f/F224-2/checkpoint-alr-5-gen-3/49946/5332810</t>
+  </si>
+  <si>
+    <t>https://media.trekbikes.com/image/upload/w_1920,h_1440,c_pad,f_auto,fl_progressive:semi,q_auto/CheckpointALR5-26-49946-C-Primary</t>
   </si>
 </sst>
 </file>
@@ -749,7 +752,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.3">
@@ -765,7 +768,7 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.3">
@@ -773,62 +776,67 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>7</v>
+        <v>114</v>
+      </c>
+    </row>
+    <row r="6" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" t="s">
         <v>10</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
         <v>11</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>12</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>13</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>14</v>
       </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
         <v>15</v>
       </c>
-      <c r="G8" t="s">
+      <c r="H8" t="s">
         <v>16</v>
       </c>
-      <c r="H8" t="s">
-        <v>17</v>
-      </c>
       <c r="J8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="K8" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="K8" s="2" t="s">
+      <c r="L8" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="L8" s="2" t="s">
+      <c r="M8" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="M8" s="2" t="s">
+      <c r="N8" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="N8" s="2" t="s">
+      <c r="O8" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="O8" s="2" t="s">
+      <c r="P8" s="2" t="s">
         <v>16</v>
-      </c>
-      <c r="P8" s="2" t="s">
-        <v>17</v>
       </c>
       <c r="Q8" s="2"/>
       <c r="R8" s="2"/>
@@ -841,10 +849,10 @@
     </row>
     <row r="9" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" t="s">
         <v>18</v>
-      </c>
-      <c r="B9" t="s">
-        <v>19</v>
       </c>
       <c r="C9">
         <v>700</v>
@@ -875,10 +883,10 @@
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>20</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>21</v>
       </c>
       <c r="C10">
         <f>K10*10</f>
@@ -905,7 +913,7 @@
         <v>610</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K10" s="3">
         <v>49</v>
@@ -936,10 +944,10 @@
     </row>
     <row r="11" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C11">
         <f>K11</f>
@@ -966,7 +974,7 @@
         <v>72.099999999999994</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K11" s="3">
         <v>74.099999999999994</v>
@@ -997,10 +1005,10 @@
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
+        <v>23</v>
+      </c>
+      <c r="B12" s="3" t="s">
         <v>24</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>25</v>
       </c>
       <c r="C12">
         <f>K12*10</f>
@@ -1027,7 +1035,7 @@
         <v>201</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K12" s="3">
         <v>9.6</v>
@@ -1058,10 +1066,10 @@
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
+        <v>25</v>
+      </c>
+      <c r="B13" s="3" t="s">
         <v>26</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>27</v>
       </c>
       <c r="C13">
         <f t="shared" ref="C13" si="3">K13</f>
@@ -1088,7 +1096,7 @@
         <v>72.599999999999994</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="K13" s="3">
         <v>71.2</v>
@@ -1119,10 +1127,10 @@
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
+        <v>27</v>
+      </c>
+      <c r="B14" s="3" t="s">
         <v>28</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>29</v>
       </c>
       <c r="C14">
         <f t="shared" ref="C14:C22" si="9">K14*10</f>
@@ -1149,7 +1157,7 @@
         <v>604</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K14" s="3">
         <v>53.6</v>
@@ -1180,10 +1188,10 @@
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="3" t="s">
         <v>30</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>31</v>
       </c>
       <c r="C15">
         <f t="shared" si="9"/>
@@ -1210,7 +1218,7 @@
         <v>74</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K15" s="3">
         <v>7.8</v>
@@ -1233,10 +1241,10 @@
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
+        <v>31</v>
+      </c>
+      <c r="B16" t="s">
         <v>32</v>
-      </c>
-      <c r="B16" t="s">
-        <v>33</v>
       </c>
       <c r="C16">
         <f t="shared" si="9"/>
@@ -1263,7 +1271,7 @@
         <v>435</v>
       </c>
       <c r="J16" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K16">
         <v>43.5</v>
@@ -1286,10 +1294,10 @@
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
+        <v>33</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>34</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>35</v>
       </c>
       <c r="C17">
         <f t="shared" si="9"/>
@@ -1316,7 +1324,7 @@
         <v>49</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K17" s="3">
         <v>4.9000000000000004</v>
@@ -1339,10 +1347,10 @@
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
+        <v>35</v>
+      </c>
+      <c r="B18" s="2" t="s">
         <v>36</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>37</v>
       </c>
       <c r="C18">
         <f t="shared" si="9"/>
@@ -1369,7 +1377,7 @@
         <v>65</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K18" s="3">
         <v>7.4</v>
@@ -1392,10 +1400,10 @@
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
+        <v>37</v>
+      </c>
+      <c r="B19" s="2" t="s">
         <v>38</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>39</v>
       </c>
       <c r="C19">
         <f t="shared" si="9"/>
@@ -1422,7 +1430,7 @@
         <v>1070</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K19" s="3">
         <v>102.5</v>
@@ -1445,10 +1453,10 @@
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
+        <v>39</v>
+      </c>
+      <c r="B20" s="2" t="s">
         <v>40</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>41</v>
       </c>
       <c r="C20">
         <f t="shared" si="9"/>
@@ -1475,7 +1483,7 @@
         <v>859</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K20" s="3">
         <v>73.5</v>
@@ -1498,10 +1506,10 @@
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
+        <v>41</v>
+      </c>
+      <c r="B21" s="2" t="s">
         <v>42</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>43</v>
       </c>
       <c r="C21">
         <f t="shared" si="9"/>
@@ -1528,7 +1536,7 @@
         <v>408</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K21" s="3">
         <v>38</v>
@@ -1551,10 +1559,10 @@
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
+        <v>43</v>
+      </c>
+      <c r="B22" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>45</v>
       </c>
       <c r="C22">
         <f t="shared" si="9"/>
@@ -1581,7 +1589,7 @@
         <v>650</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K22" s="3">
         <v>54.5</v>
@@ -1604,7 +1612,7 @@
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B23" s="2"/>
       <c r="J23" s="2"/>
@@ -1617,10 +1625,10 @@
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B24" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C24">
         <v>415</v>
@@ -1650,10 +1658,10 @@
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B25" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J25" s="2"/>
       <c r="K25" s="3"/>
@@ -1665,10 +1673,10 @@
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B26" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C26">
         <v>70</v>
@@ -1698,10 +1706,10 @@
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B27" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J27" s="2"/>
       <c r="K27" s="3"/>
@@ -1713,10 +1721,10 @@
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B28" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C28">
         <v>42</v>
@@ -1746,10 +1754,10 @@
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B29" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C29">
         <v>50</v>
@@ -1779,10 +1787,10 @@
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B30" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C30">
         <v>143</v>
@@ -1812,10 +1820,10 @@
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B31" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C31">
         <v>158</v>
@@ -1838,260 +1846,260 @@
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
+        <v>55</v>
+      </c>
+      <c r="B33" t="s">
         <v>56</v>
-      </c>
-      <c r="B33" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
+        <v>106</v>
+      </c>
+      <c r="B34" t="s">
         <v>107</v>
-      </c>
-      <c r="B34" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
+        <v>108</v>
+      </c>
+      <c r="B35" t="s">
         <v>109</v>
-      </c>
-      <c r="B35" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
+        <v>110</v>
+      </c>
+      <c r="B36" t="s">
         <v>111</v>
-      </c>
-      <c r="B36" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
+        <v>58</v>
+      </c>
+      <c r="B38" t="s">
         <v>59</v>
-      </c>
-      <c r="B38" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B40" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
+        <v>63</v>
+      </c>
+      <c r="B42" t="s">
         <v>64</v>
-      </c>
-      <c r="B42" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
+        <v>68</v>
+      </c>
+      <c r="B46" t="s">
         <v>69</v>
-      </c>
-      <c r="B46" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B47" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
+        <v>71</v>
+      </c>
+      <c r="B48" t="s">
         <v>72</v>
-      </c>
-      <c r="B48" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
+        <v>74</v>
+      </c>
+      <c r="B50" t="s">
         <v>75</v>
-      </c>
-      <c r="B50" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
+        <v>76</v>
+      </c>
+      <c r="B51" t="s">
         <v>77</v>
-      </c>
-      <c r="B51" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
+        <v>78</v>
+      </c>
+      <c r="B52" t="s">
         <v>79</v>
-      </c>
-      <c r="B52" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
+        <v>80</v>
+      </c>
+      <c r="B53" t="s">
         <v>81</v>
-      </c>
-      <c r="B53" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B54" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
+        <v>84</v>
+      </c>
+      <c r="B56" t="s">
         <v>85</v>
-      </c>
-      <c r="B56" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B57" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B59" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
+        <v>90</v>
+      </c>
+      <c r="B61" t="s">
         <v>91</v>
-      </c>
-      <c r="B61" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
+        <v>92</v>
+      </c>
+      <c r="B62" t="s">
         <v>93</v>
-      </c>
-      <c r="B62" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B63" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B64" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B65" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B68">
         <v>1049.99</v>
@@ -2099,7 +2107,7 @@
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B69">
         <v>1499.99</v>
@@ -2107,15 +2115,15 @@
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
+        <v>102</v>
+      </c>
+      <c r="B71" t="s">
         <v>103</v>
-      </c>
-      <c r="B71" t="s">
-        <v>104</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Trek Checkpoint ALR (gen 3) 2025.xlsx
+++ b/data/gravel/Trek Checkpoint ALR (gen 3) 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49FBB5B8-0654-6F42-9B4D-6FE0C1A9B6F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85441765-244D-3E41-BD1B-148DAA1A0B26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="34780" yWindow="-21340" windowWidth="26600" windowHeight="13160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="118">
   <si>
     <t>brand</t>
   </si>
@@ -344,9 +344,6 @@
     <t>currency</t>
   </si>
   <si>
-    <t>us</t>
-  </si>
-  <si>
     <t>aluminum</t>
   </si>
   <si>
@@ -381,6 +378,15 @@
   </si>
   <si>
     <t>https://media.trekbikes.com/image/upload/w_1920,h_1440,c_pad,f_auto,fl_progressive:semi,q_auto/CheckpointALR5-26-49946-C-Primary</t>
+  </si>
+  <si>
+    <t>USD</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Waterloo, Wisconsin, USA</t>
   </si>
 </sst>
 </file>
@@ -733,7 +739,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:X71"/>
+  <dimension ref="A1:X72"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -752,7 +758,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.3">
@@ -776,12 +782,12 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.3">
@@ -789,7 +795,7 @@
         <v>8</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.3">
@@ -1612,7 +1618,7 @@
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B23" s="2"/>
       <c r="J23" s="2"/>
@@ -1854,26 +1860,26 @@
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
+        <v>105</v>
+      </c>
+      <c r="B34" t="s">
         <v>106</v>
-      </c>
-      <c r="B34" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
+        <v>107</v>
+      </c>
+      <c r="B35" t="s">
         <v>108</v>
-      </c>
-      <c r="B35" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
+        <v>109</v>
+      </c>
+      <c r="B36" t="s">
         <v>110</v>
-      </c>
-      <c r="B36" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
@@ -1881,7 +1887,7 @@
         <v>57</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
@@ -2123,7 +2129,15 @@
         <v>102</v>
       </c>
       <c r="B71" t="s">
-        <v>103</v>
+        <v>115</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>116</v>
+      </c>
+      <c r="B72" t="s">
+        <v>117</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Trek Checkpoint ALR (gen 3) 2025.xlsx
+++ b/data/gravel/Trek Checkpoint ALR (gen 3) 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85441765-244D-3E41-BD1B-148DAA1A0B26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD126035-282E-B646-8871-BCFBB20D54E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="124">
   <si>
     <t>brand</t>
   </si>
@@ -387,6 +387,24 @@
   </si>
   <si>
     <t>Waterloo, Wisconsin, USA</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -739,7 +757,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:X72"/>
+  <dimension ref="A1:X78"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1957,131 +1975,116 @@
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>71</v>
-      </c>
-      <c r="B48" t="s">
-        <v>72</v>
+        <v>118</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>73</v>
+        <v>119</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>74</v>
-      </c>
-      <c r="B50" t="s">
-        <v>75</v>
+        <v>120</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>76</v>
-      </c>
-      <c r="B51" t="s">
-        <v>77</v>
+        <v>121</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>78</v>
-      </c>
-      <c r="B52" t="s">
-        <v>79</v>
+        <v>122</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>80</v>
-      </c>
-      <c r="B53" t="s">
-        <v>81</v>
+        <v>123</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="B54" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="B56" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="B57" t="s">
-        <v>59</v>
+        <v>77</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>87</v>
+        <v>78</v>
+      </c>
+      <c r="B58" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="B59" t="s">
-        <v>59</v>
+        <v>81</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>89</v>
+        <v>82</v>
+      </c>
+      <c r="B60" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>90</v>
-      </c>
-      <c r="B61" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="B62" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="B63" t="s">
-        <v>93</v>
+        <v>59</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>95</v>
-      </c>
-      <c r="B64" t="s">
-        <v>59</v>
+        <v>87</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="B65" t="s">
         <v>59</v>
@@ -2089,54 +2092,99 @@
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>97</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>59</v>
+        <v>89</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>98</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>59</v>
+        <v>90</v>
+      </c>
+      <c r="B67" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>99</v>
-      </c>
-      <c r="B68">
-        <v>1049.99</v>
+        <v>92</v>
+      </c>
+      <c r="B68" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>100</v>
-      </c>
-      <c r="B69">
-        <v>1499.99</v>
+        <v>94</v>
+      </c>
+      <c r="B69" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>101</v>
+        <v>95</v>
+      </c>
+      <c r="B70" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="B71" t="s">
-        <v>115</v>
+        <v>59</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
+        <v>97</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>98</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>99</v>
+      </c>
+      <c r="B74">
+        <v>1049.99</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>100</v>
+      </c>
+      <c r="B75">
+        <v>1499.99</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>102</v>
+      </c>
+      <c r="B77" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
         <v>116</v>
       </c>
-      <c r="B72" t="s">
+      <c r="B78" t="s">
         <v>117</v>
       </c>
     </row>
